--- a/ICASSP27_birds.xlsx
+++ b/ICASSP27_birds.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">fl_aachen_avocet_may2026_data</t>
   </si>
   <si>
-    <t xml:space="preserve">fl_aachen_avocets_may2026</t>
+    <t xml:space="preserve">fl_aachen_avocets_may2026_data</t>
   </si>
   <si>
     <t xml:space="preserve">Scarlet ibis</t>
